--- a/STEPS_data_analysis/templates/template_data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/template_data_fromR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\STEPS_data_analysis\excel_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B306E4DC-F12B-4D53-9E00-1BBF3E93CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC623386-F767-479C-A423-00BF1D78C0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="1500" windowWidth="14670" windowHeight="13020" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="329">
   <si>
     <t>ind_level</t>
   </si>
@@ -114,21 +114,12 @@
     <t>Raised Total Cholesterol</t>
   </si>
   <si>
-    <t>of men have low HDL (good cholesterol)</t>
-  </si>
-  <si>
-    <t>of women have low HDL (good cholesterol)</t>
-  </si>
-  <si>
     <t>Cardiovascular Disease</t>
   </si>
   <si>
     <t>Multiple Risk Factors</t>
   </si>
   <si>
-    <t>of the population have 0 risk factors</t>
-  </si>
-  <si>
     <t>english</t>
   </si>
   <si>
@@ -423,9 +414,6 @@
     <t>hours</t>
   </si>
   <si>
-    <t>of the population have raised blood pressure or are currently on medication for raised blood pressure</t>
-  </si>
-  <si>
     <t>Of those …</t>
   </si>
   <si>
@@ -441,18 +429,12 @@
     <t>bm1d1</t>
   </si>
   <si>
-    <t>of the population have raised blood sugar or are currently on medication for diabetes</t>
-  </si>
-  <si>
     <t>are currently receiving treatment</t>
   </si>
   <si>
     <t>of the population have never had their blood sugar measured</t>
   </si>
   <si>
-    <t>of the population have raised total cholesterol</t>
-  </si>
-  <si>
     <t>bm17c1</t>
   </si>
   <si>
@@ -495,12 +477,6 @@
     <t>were advised to maintain healthy weight/lose weight</t>
   </si>
   <si>
-    <t>of the population have 3 to 5 risk factors</t>
-  </si>
-  <si>
-    <t>of the population have 1to 2 risk factors</t>
-  </si>
-  <si>
     <t>of 18-44 year olds have 3 to 5 risk factors</t>
   </si>
   <si>
@@ -636,9 +612,6 @@
     <t>Pression artérielle élevée</t>
   </si>
   <si>
-    <t>de la population souffre d'hypertension artérielle ou prend actuellement des médicaments pour traiter l'hypertension</t>
-  </si>
-  <si>
     <t>Parmi ceux-ci…</t>
   </si>
   <si>
@@ -654,24 +627,12 @@
     <t>glycémie élevée</t>
   </si>
   <si>
-    <t>de la population présente une glycémie élevée ou prend actuellement des médicaments contre le diabète</t>
-  </si>
-  <si>
     <t>reçoivent actuellement un traitement</t>
   </si>
   <si>
     <t>de la population n'a jamais eu sa glycémie mesurée</t>
   </si>
   <si>
-    <t>de la population présente un taux de cholestérol total élevé</t>
-  </si>
-  <si>
-    <t>des hommes ont un faible taux de HDL (bon cholestérol)</t>
-  </si>
-  <si>
-    <t>des femmes ont un faible taux de HDL (bon cholestérol)</t>
-  </si>
-  <si>
     <t>de la population âgée de 40 à 69 ans présente un risque de MCV à 10 ans ≥ 20 % ou souffre déjà d'une MCV</t>
   </si>
   <si>
@@ -705,15 +666,6 @@
     <t>ont été conseillés de maintenir un poids santé/de perdre du poids</t>
   </si>
   <si>
-    <t>de la population présentent 3 à 5 facteurs de risque</t>
-  </si>
-  <si>
-    <t>de la population présentent 1 à 2 facteurs de risque</t>
-  </si>
-  <si>
-    <t>de la population ne présente aucun facteur de risque</t>
-  </si>
-  <si>
     <t>des personnes âgées de 18 à 44 ans présentent de 3 à 5 facteurs de risque</t>
   </si>
   <si>
@@ -736,6 +688,342 @@
   </si>
   <si>
     <t>of the population aged 18-69 have 1 to 2 risk factors</t>
+  </si>
+  <si>
+    <t>spanish</t>
+  </si>
+  <si>
+    <t>Consumo de tabaco</t>
+  </si>
+  <si>
+    <t>de la población son fumadores actuales</t>
+  </si>
+  <si>
+    <t>de las mujeres</t>
+  </si>
+  <si>
+    <t>de los hombres</t>
+  </si>
+  <si>
+    <t>Entre los fumadores actuales</t>
+  </si>
+  <si>
+    <t>fuman a diario</t>
+  </si>
+  <si>
+    <t>fuman cigarrillos manufacturados</t>
+  </si>
+  <si>
+    <t>fuman cigarrillos armados</t>
+  </si>
+  <si>
+    <t>fuman puros o puritos</t>
+  </si>
+  <si>
+    <t>fuman pipa</t>
+  </si>
+  <si>
+    <t>fuman pipa de agua</t>
+  </si>
+  <si>
+    <t>intentaron dejar de fumar en los últimos 12 meses</t>
+  </si>
+  <si>
+    <t>recibieron consejo de de dejar de fumar por parte de un profesional de salud</t>
+  </si>
+  <si>
+    <t>de la población son usuarios de tabaco sin humo</t>
+  </si>
+  <si>
+    <t>de la población usan cualquier producto de tabaco</t>
+  </si>
+  <si>
+    <t>Consumo de alcohol</t>
+  </si>
+  <si>
+    <t>de la población son bebedores actuales</t>
+  </si>
+  <si>
+    <t>de 18-44 años</t>
+  </si>
+  <si>
+    <t>de 45-69 años</t>
+  </si>
+  <si>
+    <t>son bebedores actuales</t>
+  </si>
+  <si>
+    <t>de la población son abstemios de toda la vida</t>
+  </si>
+  <si>
+    <t>Consumo episódico excesivo</t>
+  </si>
+  <si>
+    <t>de la población consumió 6 o más bebidas en una ocasión en los últimos 30 días</t>
+  </si>
+  <si>
+    <t>de los hombres consumió 6 o más bebidas en una ocasión</t>
+  </si>
+  <si>
+    <t>de las mujeres consumió 6 o más bebidas en una ocasión</t>
+  </si>
+  <si>
+    <t>Alimentación</t>
+  </si>
+  <si>
+    <t>días</t>
+  </si>
+  <si>
+    <t>número medio de días de consumo de frutas en una semana típica</t>
+  </si>
+  <si>
+    <t>número medio de días de consumo de verduras en una semana típica</t>
+  </si>
+  <si>
+    <t>de la población come menos de 5 porciones de frutas y/o verduras al día</t>
+  </si>
+  <si>
+    <t>de la población no come ninguna fruta ni verdura</t>
+  </si>
+  <si>
+    <t>de la población come siempre o con frecuencia alimentos procesados con alto contenido de sal</t>
+  </si>
+  <si>
+    <t>número medio de gramos de sal consumidos por día</t>
+  </si>
+  <si>
+    <t>Actividad física</t>
+  </si>
+  <si>
+    <t>de la población no cumple las recomendaciones de la OMS sobre actividad física</t>
+  </si>
+  <si>
+    <t>Entre las mujeres…</t>
+  </si>
+  <si>
+    <t>Entre los hombres…</t>
+  </si>
+  <si>
+    <t>no cumple las recomendaciones de la OMS sobre actividad física</t>
+  </si>
+  <si>
+    <t>no realiza actividad física vigorosa</t>
+  </si>
+  <si>
+    <t>de la población no realiza actividad física en el trabajo</t>
+  </si>
+  <si>
+    <t>de la población no realiza actividad física para transportarse, como caminar o bicicleta</t>
+  </si>
+  <si>
+    <t>de la población no realiza actividad física en su tiempo libre</t>
+  </si>
+  <si>
+    <t>Tiempo promedio de actividades sedentarias al día</t>
+  </si>
+  <si>
+    <t>minutos</t>
+  </si>
+  <si>
+    <t>horas</t>
+  </si>
+  <si>
+    <t>Índice de masa corporal</t>
+  </si>
+  <si>
+    <t>de la población tiene sobrepeso</t>
+  </si>
+  <si>
+    <t>de los hombres tienen sobrepeso</t>
+  </si>
+  <si>
+    <t>de las mujeres tienen sobrepeso</t>
+  </si>
+  <si>
+    <t>de la población tienen obesidad</t>
+  </si>
+  <si>
+    <t>de los hombres tienen obesidad</t>
+  </si>
+  <si>
+    <t>de las mujeres tienen obesidad</t>
+  </si>
+  <si>
+    <t>Presión arterial elevada</t>
+  </si>
+  <si>
+    <t>De estos...</t>
+  </si>
+  <si>
+    <t>fueron previamente diagnosticados con presión arterial elevada (conocen)</t>
+  </si>
+  <si>
+    <t>toman medicación para la presión arterial elevada (tratados)</t>
+  </si>
+  <si>
+    <t>tienen su presión arterial controlada (controlados)</t>
+  </si>
+  <si>
+    <t>Glucemia elevada</t>
+  </si>
+  <si>
+    <t>están en tratamiento en la actualidad</t>
+  </si>
+  <si>
+    <t>de la población nunca se midió la glucosa en sangre</t>
+  </si>
+  <si>
+    <t>Colesterol total elevado</t>
+  </si>
+  <si>
+    <t>Enfermedades cardiovasculares</t>
+  </si>
+  <si>
+    <t>de la población de 40 a 69 años tiene un riesgo de ECV a 10 años ≥20% o tiene ECV existente</t>
+  </si>
+  <si>
+    <t>de los cuales</t>
+  </si>
+  <si>
+    <t>reciben terapia farmacológica y asesoramiento para prevenir ataques cardíacos y ataques cerebrovasculares</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> recibieron consejo de dejar de consumir tabaco o no comienzar</t>
+  </si>
+  <si>
+    <t>recibieron consejo de reducir la sal en la dieta</t>
+  </si>
+  <si>
+    <t>recibieron consejo de comer al menos cinco porciones de frutas y verduras al día</t>
+  </si>
+  <si>
+    <t>recibieron consejo de reducir la grasa en la dieta</t>
+  </si>
+  <si>
+    <t>recibieron consejo de hacer más actividad física</t>
+  </si>
+  <si>
+    <t>recibieron consejo de mantener un peso saludable/perder peso</t>
+  </si>
+  <si>
+    <t>recibieron consejo de reducir las bebidas azucaradas en la dieta</t>
+  </si>
+  <si>
+    <t>Factores de riesgo múltiples</t>
+  </si>
+  <si>
+    <t>de la población 18-44 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la población 45-69 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 0 factores de riesgo</t>
+  </si>
+  <si>
+    <t>Consejería de estilo de vida*</t>
+  </si>
+  <si>
+    <t>*consejos recibidos durante los últimos 12 meses por parte de un médico o profesional de la salud, entre toda la población</t>
+  </si>
+  <si>
+    <t>* IMC ≥ 25</t>
+  </si>
+  <si>
+    <t>** IMC ≥ 30</t>
+  </si>
+  <si>
+    <t>* PAS ≥ 140 et/ou PAD ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t>* PAS ≥ 140 y/o PAD ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t>* BMI ≥ 25</t>
+  </si>
+  <si>
+    <t>** BMI ≥ 30</t>
+  </si>
+  <si>
+    <t>* SBP ≥ 140 and/or DBP ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t>* ≥ 126 mg/dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* ≥ 190 mg/dl </t>
+  </si>
+  <si>
+    <t>** &lt; 40 mg/d</t>
+  </si>
+  <si>
+    <t>*** &lt; 50 mg/d</t>
+  </si>
+  <si>
+    <t>of the population are overweight*</t>
+  </si>
+  <si>
+    <t>of the population are obese**</t>
+  </si>
+  <si>
+    <t>of the population have raised blood pressure* or are currently on medication for raised blood pressure</t>
+  </si>
+  <si>
+    <t>de la population souffre d'hypertension artérielle* ou prend actuellement des médicaments pour traiter l'hypertension</t>
+  </si>
+  <si>
+    <t>de la población tiene presión arterial elevada* o toma medicación para la presión arterial elevada</t>
+  </si>
+  <si>
+    <t>of the population have raised blood sugar* or are currently on medication for diabetes</t>
+  </si>
+  <si>
+    <t>de la population présente une glycémie élevée* ou prend actuellement des médicaments contre le diabète</t>
+  </si>
+  <si>
+    <t>de la población tiene la glucosa en sangre elevada* o está en tratamiento para diabetes</t>
+  </si>
+  <si>
+    <t>of the population have raised total cholesterol*</t>
+  </si>
+  <si>
+    <t>of men have low HDL (good cholesterol)**</t>
+  </si>
+  <si>
+    <t>of women have low HDL (good cholesterol)***</t>
+  </si>
+  <si>
+    <t>de la population présente un taux de cholestérol total élevé*</t>
+  </si>
+  <si>
+    <t>des hommes ont un faible taux de HDL (bon cholestérol)**</t>
+  </si>
+  <si>
+    <t>des femmes ont un faible taux de HDL (bon cholestérol)***</t>
+  </si>
+  <si>
+    <t>de la población tiene el colesterol total elevado*</t>
+  </si>
+  <si>
+    <t>de los hombres tienen bajo el colesterol HDL (colesterol bueno)**</t>
+  </si>
+  <si>
+    <t>de las mujeres tienen bajo el colesterol HDL (colesterol bueno)***</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773036CE-016D-FE40-B5BF-2775730B9CD1}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
@@ -1173,34 +1461,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>2</v>
@@ -1208,10 +1496,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
@@ -1219,81 +1507,81 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -1301,35 +1589,35 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,21 +1627,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2</v>
@@ -1361,10 +1649,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -1372,10 +1660,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>6</v>
@@ -1383,10 +1671,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>7</v>
@@ -1394,15 +1682,15 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
@@ -1410,26 +1698,26 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>9</v>
@@ -1437,10 +1725,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>10</v>
@@ -1453,37 +1741,37 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C32" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>12</v>
@@ -1491,10 +1779,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>13</v>
@@ -1502,24 +1790,24 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1529,121 +1817,121 @@
     </row>
     <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C52" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C53" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1653,21 +1941,21 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>21</v>
@@ -1675,10 +1963,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>20</v>
@@ -1686,21 +1974,21 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>16</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>18</v>
@@ -1708,328 +1996,366 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>17</v>
       </c>
     </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C65" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>74</v>
-      </c>
-      <c r="B64" t="s">
-        <v>45</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>130</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" t="s">
-        <v>45</v>
-      </c>
       <c r="C67" s="7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="7"/>
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="2" t="s">
+      <c r="A70" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C71" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C73" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>133</v>
-      </c>
-      <c r="B71" t="s">
-        <v>45</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" t="s">
-        <v>45</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" t="s">
-        <v>45</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="7"/>
+    <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="2" t="s">
-        <v>24</v>
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>213</v>
+      </c>
+      <c r="B80" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B81" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B82" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="8"/>
+      <c r="C83" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="8"/>
+      <c r="C84" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="8"/>
+      <c r="C85" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C87" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C89" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C92" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+    <row r="93" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C93" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B77" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94" t="s">
+        <v>42</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B78" t="s">
-        <v>47</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>93</v>
-      </c>
-      <c r="B81" t="s">
-        <v>45</v>
-      </c>
-      <c r="C81" s="7" t="s">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B95" t="s">
+        <v>42</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>78</v>
+      </c>
+      <c r="B96" t="s">
+        <v>42</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" t="s">
-        <v>45</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" t="s">
-        <v>45</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>83</v>
-      </c>
-      <c r="B88" t="s">
-        <v>45</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" t="s">
-        <v>45</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>84</v>
-      </c>
-      <c r="B90" t="s">
-        <v>45</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" t="s">
-        <v>45</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" t="s">
-        <v>45</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>82</v>
-      </c>
-      <c r="B93" t="s">
-        <v>45</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96" t="s">
-        <v>45</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B97" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>232</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B98" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>231</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B99" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>155</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C102" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>75</v>
+      </c>
+      <c r="B104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>76</v>
+      </c>
+      <c r="B105" t="s">
+        <v>42</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>74</v>
+      </c>
+      <c r="B106" t="s">
+        <v>52</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" t="s">
+        <v>53</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2040,739 +2366,1089 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14325372-24F7-AD49-AB77-733D60DE2475}">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.625" customWidth="1"/>
     <col min="2" max="2" width="81.75" customWidth="1"/>
+    <col min="3" max="3" width="58.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="C7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
-      <c r="B8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
-      <c r="B9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>102</v>
-      </c>
       <c r="B12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="C12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="C13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B44" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="C51" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="7" t="s">
+      <c r="C88" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="7" t="s">
+      <c r="C90" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="C92" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="7" t="s">
+      <c r="C93" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="7" t="s">
+      <c r="C94" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" s="2" t="s">
+      <c r="C96" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B100" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B77" s="7" t="s">
+      <c r="C100" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B106" s="7" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B78" s="7" t="s">
+      <c r="C106" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>226</v>
+      <c r="C107" s="7" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/STEPS_data_analysis/templates/template_data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/template_data_fromR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\Latest from Lucas\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC623386-F767-479C-A423-00BF1D78C0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6710C2B-90D6-4913-9A4D-1FF3A8500528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="329">
   <si>
     <t>ind_level</t>
   </si>
@@ -87,18 +87,12 @@
     <t>Body Mass Index</t>
   </si>
   <si>
-    <t>of the population are obese</t>
-  </si>
-  <si>
     <t>of women are obese</t>
   </si>
   <si>
     <t>of men are obese</t>
   </si>
   <si>
-    <t>of the population are overweight</t>
-  </si>
-  <si>
     <t>of women are overweight</t>
   </si>
   <si>
@@ -603,12 +597,6 @@
     <t>heures</t>
   </si>
   <si>
-    <t>de la population est en surpoids</t>
-  </si>
-  <si>
-    <t>de la population est obèse</t>
-  </si>
-  <si>
     <t>Pression artérielle élevée</t>
   </si>
   <si>
@@ -831,18 +819,12 @@
     <t>Índice de masa corporal</t>
   </si>
   <si>
-    <t>de la población tiene sobrepeso</t>
-  </si>
-  <si>
     <t>de los hombres tienen sobrepeso</t>
   </si>
   <si>
     <t>de las mujeres tienen sobrepeso</t>
   </si>
   <si>
-    <t>de la población tienen obesidad</t>
-  </si>
-  <si>
     <t>de los hombres tienen obesidad</t>
   </si>
   <si>
@@ -1024,6 +1006,24 @@
   </si>
   <si>
     <t>de las mujeres tienen bajo el colesterol HDL (colesterol bueno)***</t>
+  </si>
+  <si>
+    <t>de la population est en surpoids*</t>
+  </si>
+  <si>
+    <t>de la población tiene sobrepeso*</t>
+  </si>
+  <si>
+    <t>de la population est obèse**</t>
+  </si>
+  <si>
+    <t>de la población tienen obesidad**</t>
+  </si>
+  <si>
+    <t>* current daily smoking, &lt;5 servings of fruit or vegetables per day, not meeting WHO recommendations for physical activity, BMI≥25, raised blood pressure (SBP ≥ 140 and/or DBP ≥ 90 mmHg or currently on medication)</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors*</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773036CE-016D-FE40-B5BF-2775730B9CD1}">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
@@ -1461,34 +1461,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>2</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>3</v>
@@ -1507,81 +1507,81 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -1589,35 +1589,35 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1627,21 +1627,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>2</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>6</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>7</v>
@@ -1682,15 +1682,15 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
@@ -1698,26 +1698,26 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>9</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>10</v>
@@ -1741,37 +1741,37 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C32" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>12</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>13</v>
@@ -1790,24 +1790,24 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1817,121 +1817,121 @@
     </row>
     <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C52" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C53" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1941,137 +1941,137 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C63" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C67" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C71" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2079,45 +2079,45 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C73" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C77" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2125,237 +2125,242 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C79" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="8"/>
       <c r="C83" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="8"/>
       <c r="C84" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="8"/>
       <c r="C85" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B94" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B98" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B99" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B100" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B103" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B104" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B105" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B106" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B107" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2376,35 +2381,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2412,10 +2417,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2423,87 +2428,87 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2511,43 +2516,43 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2555,21 +2560,21 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2577,10 +2582,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2588,10 +2593,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,10 +2604,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2610,21 +2615,21 @@
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,32 +2637,32 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2665,10 +2670,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2676,10 +2681,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2687,43 +2692,43 @@
         <v>11</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2731,10 +2736,10 @@
         <v>12</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2742,32 +2747,32 @@
         <v>13</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,153 +2780,153 @@
         <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2929,175 +2934,175 @@
         <v>15</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>188</v>
+        <v>323</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>16</v>
+        <v>307</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>189</v>
+        <v>325</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3107,57 +3112,57 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,288 +3172,288 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/STEPS_data_analysis/templates/template_data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/template_data_fromR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\Latest from Lucas\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\most recent from Lucas\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6710C2B-90D6-4913-9A4D-1FF3A8500528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9AABE7-434E-4DEA-B2CA-8F793493DA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
+    <workbookView xWindow="2175" yWindow="0" windowWidth="20370" windowHeight="14670" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="328">
   <si>
     <t>ind_level</t>
   </si>
@@ -669,9 +669,6 @@
     <t>bm1l1</t>
   </si>
   <si>
-    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
-  </si>
-  <si>
     <t>of the population aged 18-69 have 0 risk factors</t>
   </si>
   <si>
@@ -903,15 +900,9 @@
     <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
   </si>
   <si>
-    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
-  </si>
-  <si>
     <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
   </si>
   <si>
-    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
-  </si>
-  <si>
     <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
   </si>
   <si>
@@ -1024,6 +1015,12 @@
   </si>
   <si>
     <t>of the population aged 18-69 have 3 to 5 risk factors*</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque*</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo*</t>
   </si>
 </sst>
 </file>
@@ -1947,7 +1944,7 @@
         <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1980,7 +1977,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2007,12 +2004,12 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C63" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2028,7 +2025,7 @@
         <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2071,7 +2068,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C71" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2090,7 +2087,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2117,7 +2114,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2136,7 +2133,7 @@
         <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2147,7 +2144,7 @@
         <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2158,25 +2155,25 @@
         <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="8"/>
       <c r="C83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="8"/>
       <c r="C84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="8"/>
       <c r="C85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2311,7 +2308,7 @@
         <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2322,7 +2319,7 @@
         <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2333,7 +2330,7 @@
         <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2360,7 +2357,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2387,7 +2384,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2398,7 +2395,7 @@
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,7 +2406,7 @@
         <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,7 +2417,7 @@
         <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2431,7 +2428,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,7 +2439,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,7 +2450,7 @@
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,7 +2461,7 @@
         <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,7 +2472,7 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,7 +2483,7 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2497,7 +2494,7 @@
         <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,7 +2505,7 @@
         <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2519,7 +2516,7 @@
         <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2530,7 +2527,7 @@
         <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2541,7 +2538,7 @@
         <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2552,7 +2549,7 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,7 +2560,7 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,7 +2571,7 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,7 +2582,7 @@
         <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,7 +2593,7 @@
         <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,7 +2604,7 @@
         <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,7 +2615,7 @@
         <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,7 +2626,7 @@
         <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,7 +2637,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,7 +2648,7 @@
         <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2662,7 +2659,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2673,7 +2670,7 @@
         <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2684,7 +2681,7 @@
         <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,7 +2692,7 @@
         <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2706,7 +2703,7 @@
         <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2717,7 +2714,7 @@
         <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,7 +2725,7 @@
         <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2739,7 +2736,7 @@
         <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,7 +2747,7 @@
         <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2761,7 +2758,7 @@
         <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,7 +2769,7 @@
         <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,7 +2780,7 @@
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2794,7 +2791,7 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,7 +2802,7 @@
         <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,7 +2813,7 @@
         <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,7 +2824,7 @@
         <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,7 +2835,7 @@
         <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,7 +2846,7 @@
         <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,7 +2857,7 @@
         <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,7 +2868,7 @@
         <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -2882,7 +2879,7 @@
         <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,7 +2890,7 @@
         <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,7 +2901,7 @@
         <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,7 +2912,7 @@
         <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,7 +2923,7 @@
         <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,18 +2934,18 @@
         <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,7 +2956,7 @@
         <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,18 +2967,18 @@
         <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,7 +2989,7 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,29 +3000,29 @@
         <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,18 +3033,18 @@
         <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,7 +3055,7 @@
         <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -3069,7 +3066,7 @@
         <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,7 +3077,7 @@
         <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,18 +3088,18 @@
         <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3118,18 +3115,18 @@
         <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3140,7 +3137,7 @@
         <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3151,18 +3148,18 @@
         <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,73 +3175,73 @@
         <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="C82" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3255,7 +3252,7 @@
         <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -3266,7 +3263,7 @@
         <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3277,7 +3274,7 @@
         <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -3288,7 +3285,7 @@
         <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3299,7 +3296,7 @@
         <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -3310,7 +3307,7 @@
         <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3321,7 +3318,7 @@
         <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,7 +3329,7 @@
         <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
@@ -3343,7 +3340,7 @@
         <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3354,7 +3351,7 @@
         <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3365,7 +3362,7 @@
         <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3376,7 +3373,7 @@
         <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3387,7 +3384,7 @@
         <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3398,40 +3395,40 @@
         <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>290</v>
+        <v>327</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3442,7 +3439,7 @@
         <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,7 +3450,7 @@
         <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/STEPS_data_analysis/templates/template_data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/template_data_fromR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\most recent from Lucas\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9AABE7-434E-4DEA-B2CA-8F793493DA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBD10E7-37A9-41F6-B6F2-02B21735EF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="0" windowWidth="20370" windowHeight="14670" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8873D99E-472C-1247-B72B-045F9E2BE3D4}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="329">
   <si>
     <t>ind_level</t>
   </si>
@@ -669,6 +669,9 @@
     <t>bm1l1</t>
   </si>
   <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
+  </si>
+  <si>
     <t>of the population aged 18-69 have 0 risk factors</t>
   </si>
   <si>
@@ -900,9 +903,15 @@
     <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
   </si>
   <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
+  </si>
+  <si>
     <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
   </si>
   <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
     <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
   </si>
   <si>
@@ -1015,12 +1024,6 @@
   </si>
   <si>
     <t>of the population aged 18-69 have 3 to 5 risk factors*</t>
-  </si>
-  <si>
-    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque*</t>
-  </si>
-  <si>
-    <t>de la población 18-69 tiene 3 a 5 factores de riesgo*</t>
   </si>
 </sst>
 </file>
@@ -1443,14 +1446,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{773036CE-016D-FE40-B5BF-2775730B9CD1}">
   <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="58.625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" customWidth="1"/>
     <col min="4" max="4" width="11" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1464,12 +1467,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1480,7 +1483,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -1491,7 +1494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -1502,12 +1505,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -1518,7 +1521,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1540,7 +1543,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1551,7 +1554,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1584,7 +1587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1606,7 +1609,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -1617,12 +1620,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1633,7 +1636,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1644,7 +1647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1655,7 +1658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1677,12 +1680,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C24" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1693,12 +1696,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C26" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1709,7 +1712,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1731,17 +1734,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C32" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1752,7 +1755,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -1763,7 +1766,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -1774,7 +1777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -1796,7 +1799,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -1807,12 +1810,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C40" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -1823,17 +1826,17 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C42" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C43" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -1855,7 +1858,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -1877,7 +1880,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>64</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -1910,7 +1913,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -1921,22 +1924,22 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C52" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C53" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C55" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -1944,10 +1947,10 @@
         <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -1969,7 +1972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1977,10 +1980,10 @@
         <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -1991,7 +1994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -2002,22 +2005,22 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C62" s="3" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C63" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C65" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -2025,15 +2028,15 @@
         <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C67" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -2044,7 +2047,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2066,20 +2069,20 @@
         <v>126</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C71" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C72" s="7"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C73" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>127</v>
       </c>
@@ -2087,10 +2090,10 @@
         <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>90</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -2112,20 +2115,20 @@
         <v>129</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C77" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C78" s="7"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C79" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -2133,10 +2136,10 @@
         <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>130</v>
       </c>
@@ -2144,10 +2147,10 @@
         <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
         <v>131</v>
       </c>
@@ -2155,33 +2158,33 @@
         <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="8"/>
       <c r="C83" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="8"/>
       <c r="C84" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="8"/>
       <c r="C85" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C87" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -2192,12 +2195,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C89" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2208,17 +2211,17 @@
         <v>134</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C92" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C93" s="7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>75</v>
       </c>
@@ -2229,7 +2232,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>78</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>76</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>81</v>
       </c>
@@ -2284,7 +2287,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -2295,12 +2298,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C102" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -2308,10 +2311,10 @@
         <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>73</v>
       </c>
@@ -2319,10 +2322,10 @@
         <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>74</v>
       </c>
@@ -2330,10 +2333,10 @@
         <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>72</v>
       </c>
@@ -2344,7 +2347,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -2355,9 +2358,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C108" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2369,14 +2372,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14325372-24F7-AD49-AB77-733D60DE2475}">
   <dimension ref="A1:C107"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="58.625" customWidth="1"/>
+    <col min="1" max="1" width="58.58203125" customWidth="1"/>
     <col min="2" max="2" width="81.75" customWidth="1"/>
-    <col min="3" max="3" width="58.625" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
@@ -2384,10 +2387,10 @@
         <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -2395,10 +2398,10 @@
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -2406,10 +2409,10 @@
         <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -2417,10 +2420,10 @@
         <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -2428,10 +2431,10 @@
         <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2439,10 +2442,10 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -2450,10 +2453,10 @@
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -2461,10 +2464,10 @@
         <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -2472,10 +2475,10 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -2483,10 +2486,10 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2494,10 +2497,10 @@
         <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>97</v>
       </c>
@@ -2505,10 +2508,10 @@
         <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -2516,10 +2519,10 @@
         <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>104</v>
       </c>
@@ -2527,10 +2530,10 @@
         <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
@@ -2538,10 +2541,10 @@
         <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>102</v>
       </c>
@@ -2549,10 +2552,10 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -2560,10 +2563,10 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -2571,10 +2574,10 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>2</v>
       </c>
@@ -2582,10 +2585,10 @@
         <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>3</v>
       </c>
@@ -2593,10 +2596,10 @@
         <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>6</v>
       </c>
@@ -2604,10 +2607,10 @@
         <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
@@ -2615,10 +2618,10 @@
         <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>105</v>
       </c>
@@ -2626,10 +2629,10 @@
         <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -2637,10 +2640,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>106</v>
       </c>
@@ -2648,10 +2651,10 @@
         <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>107</v>
       </c>
@@ -2659,10 +2662,10 @@
         <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>9</v>
       </c>
@@ -2670,10 +2673,10 @@
         <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>10</v>
       </c>
@@ -2681,10 +2684,10 @@
         <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
@@ -2692,10 +2695,10 @@
         <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>108</v>
       </c>
@@ -2703,10 +2706,10 @@
         <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -2714,10 +2717,10 @@
         <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>86</v>
       </c>
@@ -2725,10 +2728,10 @@
         <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>12</v>
       </c>
@@ -2736,10 +2739,10 @@
         <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>13</v>
       </c>
@@ -2747,10 +2750,10 @@
         <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>109</v>
       </c>
@@ -2758,10 +2761,10 @@
         <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>111</v>
       </c>
@@ -2769,10 +2772,10 @@
         <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -2780,10 +2783,10 @@
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>112</v>
       </c>
@@ -2791,10 +2794,10 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>113</v>
       </c>
@@ -2802,10 +2805,10 @@
         <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>114</v>
       </c>
@@ -2813,10 +2816,10 @@
         <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>115</v>
       </c>
@@ -2824,10 +2827,10 @@
         <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>115</v>
       </c>
@@ -2835,10 +2838,10 @@
         <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>116</v>
       </c>
@@ -2846,10 +2849,10 @@
         <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>116</v>
       </c>
@@ -2857,10 +2860,10 @@
         <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>117</v>
       </c>
@@ -2868,10 +2871,10 @@
         <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>118</v>
       </c>
@@ -2879,10 +2882,10 @@
         <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>119</v>
       </c>
@@ -2890,10 +2893,10 @@
         <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>120</v>
       </c>
@@ -2901,10 +2904,10 @@
         <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>121</v>
       </c>
@@ -2912,10 +2915,10 @@
         <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>122</v>
       </c>
@@ -2923,10 +2926,10 @@
         <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
@@ -2934,21 +2937,21 @@
         <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>19</v>
       </c>
@@ -2956,10 +2959,10 @@
         <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
         <v>18</v>
       </c>
@@ -2967,21 +2970,21 @@
         <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
         <v>17</v>
       </c>
@@ -2989,10 +2992,10 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>16</v>
       </c>
@@ -3000,32 +3003,32 @@
         <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>293</v>
-      </c>
       <c r="C63" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>20</v>
       </c>
@@ -3033,21 +3036,21 @@
         <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>123</v>
       </c>
@@ -3055,10 +3058,10 @@
         <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>124</v>
       </c>
@@ -3066,10 +3069,10 @@
         <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>125</v>
       </c>
@@ -3077,10 +3080,10 @@
         <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>126</v>
       </c>
@@ -3088,26 +3091,26 @@
         <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>21</v>
       </c>
@@ -3115,21 +3118,21 @@
         <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>128</v>
       </c>
@@ -3137,10 +3140,10 @@
         <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
         <v>129</v>
       </c>
@@ -3148,26 +3151,26 @@
         <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>22</v>
       </c>
@@ -3175,76 +3178,76 @@
         <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>23</v>
       </c>
@@ -3252,10 +3255,10 @@
         <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
         <v>132</v>
       </c>
@@ -3263,10 +3266,10 @@
         <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>133</v>
       </c>
@@ -3274,10 +3277,10 @@
         <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>134</v>
       </c>
@@ -3285,10 +3288,10 @@
         <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>135</v>
       </c>
@@ -3296,10 +3299,10 @@
         <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>136</v>
       </c>
@@ -3307,10 +3310,10 @@
         <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>137</v>
       </c>
@@ -3318,10 +3321,10 @@
         <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>140</v>
       </c>
@@ -3329,10 +3332,10 @@
         <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>138</v>
       </c>
@@ -3340,10 +3343,10 @@
         <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>141</v>
       </c>
@@ -3351,10 +3354,10 @@
         <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
         <v>142</v>
       </c>
@@ -3362,10 +3365,10 @@
         <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>143</v>
       </c>
@@ -3373,10 +3376,10 @@
         <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>139</v>
       </c>
@@ -3384,10 +3387,10 @@
         <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>24</v>
       </c>
@@ -3395,43 +3398,43 @@
         <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B105" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C104" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="C105" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>144</v>
       </c>
@@ -3439,10 +3442,10 @@
         <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>145</v>
       </c>
@@ -3450,7 +3453,7 @@
         <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
